--- a/outputs/edge_stats_90m_RAN.xlsx
+++ b/outputs/edge_stats_90m_RAN.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raenb\Documents\GitHub\madagascar\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{7D2EF854-2CF9-44A4-967D-BB5F671B6A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C21B115-CEA5-45B7-8FA1-DE36514D5555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-1035" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="edge_stats_90m" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4615,102 +4612,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="frag_stats_90m"/>
-      <sheetName val="reorganized"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>National intactness</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>CFM intactness</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>PA intactness</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>2005</v>
-          </cell>
-          <cell r="B2">
-            <v>64.819693069607993</v>
-          </cell>
-          <cell r="C2">
-            <v>73.805743493025005</v>
-          </cell>
-          <cell r="D2">
-            <v>85.0030203062054</v>
-          </cell>
-          <cell r="E2">
-            <v>30.599860180381501</v>
-          </cell>
-          <cell r="F2">
-            <v>26.087972027436098</v>
-          </cell>
-          <cell r="G2">
-            <v>21.195315081477901</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2010</v>
-          </cell>
-          <cell r="B3">
-            <v>62.8706550428412</v>
-          </cell>
-          <cell r="C3">
-            <v>71.890855151157595</v>
-          </cell>
-          <cell r="D3">
-            <v>84.299214687961097</v>
-          </cell>
-          <cell r="E3">
-            <v>30.676056084584001</v>
-          </cell>
-          <cell r="F3">
-            <v>26.758623442522801</v>
-          </cell>
-          <cell r="G3">
-            <v>21.5320632582816</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2014</v>
-          </cell>
-          <cell r="B4">
-            <v>60.617154869126999</v>
-          </cell>
-          <cell r="C4">
-            <v>69.366493733258395</v>
-          </cell>
-          <cell r="D4">
-            <v>83.329914590523302</v>
-          </cell>
-          <cell r="E4">
-            <v>30.658451814519299</v>
-          </cell>
-          <cell r="F4">
-            <v>27.279249385404899</v>
-          </cell>
-          <cell r="G4">
-            <v>21.948736070542999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5007,11 +4908,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>

--- a/outputs/edge_stats_90m_RAN.xlsx
+++ b/outputs/edge_stats_90m_RAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raenb\Documents\GitHub\madagascar\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C21B115-CEA5-45B7-8FA1-DE36514D5555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82EDB82-F110-4918-9CAA-B3FD81420B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1035" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="edge_stats_90m" sheetId="1" r:id="rId1"/>
@@ -49,19 +49,22 @@
     <t>PA SD</t>
   </si>
   <si>
-    <t>National distance to edge</t>
+    <t>National mean</t>
   </si>
   <si>
-    <t>CFM distance to edge</t>
+    <t>CFM mean</t>
   </si>
   <si>
-    <t>PA distance to edge</t>
+    <t>PA mean</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -539,8 +542,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -639,14 +643,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>National distance to edge</c:v>
+                  <c:v>National mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -730,7 +734,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$B$3:$B$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>341.186556819298</c:v>
@@ -759,14 +763,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CFM distance to edge</c:v>
+                  <c:v>CFM mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -850,7 +854,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$C$3:$C$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>377.74146537566997</c:v>
@@ -879,14 +883,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PA distance to edge</c:v>
+                  <c:v>PA mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -970,7 +974,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$D$3:$D$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>705.73855600270394</c:v>
@@ -1074,7 +1078,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Distance to forest edge (m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1251,7 +1310,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>National distance to edge</c:v>
+                  <c:v>National mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1259,7 +1318,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1270,11 +1329,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1357,7 +1416,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$B$3:$B$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>341.186556819298</c:v>
@@ -1463,7 +1522,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1609,7 +1668,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PA distance to edge</c:v>
+                  <c:v>PA mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1617,9 +1676,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1630,15 +1687,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="65000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent4"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1721,7 +1774,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$D$3:$D$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>705.73855600270394</c:v>
@@ -1827,7 +1880,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1973,7 +2026,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CFM distance to edge</c:v>
+                  <c:v>CFM mean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1981,7 +2034,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1992,11 +2045,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="accent6"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2079,7 +2132,7 @@
             <c:numRef>
               <c:f>edge_stats_90m!$C$3:$C$5</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>377.74146537566997</c:v>
@@ -2185,7 +2238,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2273,12 +2326,9 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -4964,22 +5014,22 @@
       <c r="A3">
         <v>2005</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>341.186556819298</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>377.74146537566997</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>705.73855600270394</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>593.10892699185297</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>516.41281733774395</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>845.25402512202402</v>
       </c>
     </row>
@@ -4987,22 +5037,22 @@
       <c r="A4">
         <v>2010</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>292.24138872083302</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>336.93239705176802</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>610.01065757409299</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>517.05055806710902</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>488.31343637651503</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>719.19188318391195</v>
       </c>
     </row>
@@ -5010,22 +5060,22 @@
       <c r="A5">
         <v>2014</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>244.33470097883099</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>280.73756243217099</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>522.17270735372801</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>433.25708605527097</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>401.75583895606002</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>606.82418925489696</v>
       </c>
     </row>
